--- a/webapp/public/templates/9.HIỆN TRẠNG THIẾT BỊ_TÂM.xlsx
+++ b/webapp/public/templates/9.HIỆN TRẠNG THIẾT BỊ_TÂM.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,14 +477,468 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>THT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CSG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CSG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CSG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CSG</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MANE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MANE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MANE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -499,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,14 +996,296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GPON</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>494</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPON</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPON</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GPON</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GPON</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GPON</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GPON</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GPON</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -564,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,14 +1343,296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>L2SW</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>827</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>L2SW</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>L2SW</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>L2SW</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>L2SW</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>L2SW</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>L2SW</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>L2SW</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -629,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,14 +1690,296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1524</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1638</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1625</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -694,7 +1994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,14 +2037,296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4G</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1753</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1912</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4G</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4G</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4G</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4G</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4G</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4G</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4G</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>239</t>
         </is>
       </c>
     </row>
@@ -759,7 +2341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,14 +2384,296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -824,7 +2688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,14 +2731,851 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cần Đước</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cần Giuộc</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Đức Huệ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bến Cầu</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Trảng Bàng</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tân Thạnh</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Thạnh Hóa</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Long An</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tầm Vu</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tân Trụ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Thủ Thừa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dương Minh Châu</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tân Biên</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Châu Thành</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hòa Thành</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Vĩnh Hưng</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Vĩnh Hưng</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
